--- a/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_2.xlsx
+++ b/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_2.xlsx
@@ -3626,7 +3626,7 @@
     <row r="14" ht="36" customHeight="1" s="72">
       <c r="B14" s="89" t="inlineStr">
         <is>
-          <t>최종 견적 금액 : 일금 일억구천삼백사십팔만일천팔백팔원 정(193,481,808원) (VAT 별도)</t>
+          <t>최종 견적 금액 : 일금 이억이천만원 정(220,000,000원) (VAT 별도)</t>
         </is>
       </c>
       <c r="C14" s="90" t="n"/>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="F17" s="152" t="n">
-        <v>29000000</v>
+        <v>33000000</v>
       </c>
       <c r="G17" s="103" t="n">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="F18" s="152" t="n">
-        <v>111000000</v>
+        <v>126000000</v>
       </c>
       <c r="G18" s="103" t="n">
         <v>1</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="F19" s="152" t="n">
-        <v>53481808</v>
+        <v>61000000</v>
       </c>
       <c r="G19" s="103" t="n">
         <v>1</v>
@@ -3965,7 +3965,7 @@
       <c r="B27" s="145" t="inlineStr">
         <is>
           <t>※ 비 고
-   - 본 견적은 과제 2(EWACS 복합 AI Agent 구축)의 모듈별 정액 산정안이며, 총액은 인력 기준 견적(견적서(인력) 시트)과 동일함
+   - 본 견적은 과제 2(EWACS 복합 AI Agent 구축)의 모듈별 정액 산정안이며, 총액은 인력 기준 견적(_1)과 동일함 (모듈 금액에 재경비·기술료 포함)
    - 모듈 구분·배분은 협의용 안이며, 비용 산정 방식(M/M 기반 vs 모듈별 정액)은 과업지시서 14조에 따라 협의 후 확정함
    - 상기 금액은 부가가치세(VAT) 별도이며, 계약 조건은 계약서에 따름</t>
         </is>
@@ -4013,9 +4013,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="H25:H26"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="F25:F26"/>
@@ -4023,10 +4023,10 @@
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="B25:E26"/>
     <mergeCell ref="B27:J28"/>
-    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
     <mergeCell ref="B4:F5"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="C17:D19"/>

--- a/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_2.xlsx
+++ b/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_2.xlsx
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'견적서(업무)'!$A$1:$K$30</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
@@ -3716,7 +3716,7 @@
       </c>
       <c r="H17" s="107">
         <f>F17*G17</f>
-        <v/>
+        <v>33000000</v>
       </c>
       <c r="I17" s="108" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="H18" s="107">
         <f>F18*G18</f>
-        <v/>
+        <v>126000000</v>
       </c>
       <c r="I18" s="108" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="H19" s="107">
         <f>F19*G19</f>
-        <v/>
+        <v>61000000</v>
       </c>
       <c r="I19" s="108" t="n">
         <v>0</v>
@@ -3792,11 +3792,11 @@
       </c>
       <c r="H20" s="120">
         <f>SUM(H17:H19)</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="I20" s="121">
         <f>H20</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="J20" s="122" t="n"/>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H21" s="127">
         <f>H20*0%</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I21" s="127" t="n"/>
       <c r="J21" s="128" t="n"/>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="H22" s="107">
         <f>(H20+H21)*0</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I22" s="107" t="n"/>
       <c r="J22" s="129" t="n"/>
@@ -3885,11 +3885,11 @@
       </c>
       <c r="H23" s="120">
         <f>SUM(H21:H22)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I23" s="121">
         <f>H23</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J23" s="122" t="n"/>
     </row>
@@ -3914,11 +3914,11 @@
       </c>
       <c r="H24" s="134">
         <f>H20+H23</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="I24" s="134">
         <f>I20+I23</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="J24" s="135" t="n"/>
     </row>
@@ -3935,11 +3935,11 @@
       <c r="G25" s="93" t="n"/>
       <c r="H25" s="138">
         <f>H24</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="I25" s="139">
         <f>H24</f>
-        <v/>
+        <v>220000000</v>
       </c>
       <c r="J25" s="140" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
       <c r="I26" s="143" t="n"/>
       <c r="J26" s="144">
         <f>100%-(I25/H25)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" s="72">
@@ -4013,7 +4013,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="C21:D21"/>
@@ -4021,9 +4020,10 @@
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B1:J1"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B25:E26"/>
     <mergeCell ref="B27:J28"/>
     <mergeCell ref="H25:H26"/>

--- a/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_2.xlsx
+++ b/cupia-ai-research/docs/08_계약관리/[CUPIA] EWACS_복합_AI_Agent_구축_견적서_20260731_2.xlsx
@@ -3965,8 +3965,8 @@
       <c r="B27" s="145" t="inlineStr">
         <is>
           <t>※ 비 고
-   - 본 견적은 과제 2(EWACS 복합 AI Agent 구축)의 모듈별 정액 산정안이며, 총액은 인력 기준 견적(_1)과 동일함 (모듈 금액에 재경비·기술료 포함)
-   - 모듈 구분·배분은 협의용 안이며, 비용 산정 방식(M/M 기반 vs 모듈별 정액)은 과업지시서 14조에 따라 협의 후 확정함
+   - 본 견적은 전자통관국제협력재단 'CUPIA AI 연구 과제 2026' 과제 2(EWACS 복합 AI Agent 구축)에 대한 모듈별 정액 견적임
+   - 모듈 금액에는 재경비 및 기술료가 포함되어 있음
    - 상기 금액은 부가가치세(VAT) 별도이며, 계약 조건은 계약서에 따름</t>
         </is>
       </c>
@@ -4015,18 +4015,18 @@
   <mergeCells count="17">
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B17:B19"/>
+    <mergeCell ref="H25:H26"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G25:G26"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B25:E26"/>
     <mergeCell ref="B27:J28"/>
-    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="B4:F5"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="C17:D19"/>
